--- a/artfynd/A 41279-2021 artfynd.xlsx
+++ b/artfynd/A 41279-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 41279-2021 artfynd.xlsx
+++ b/artfynd/A 41279-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>85440028</v>
+        <v>94036229</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>SO om Villmyren, Vrm</t>
+          <t>Sydväst om Branäsberget, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>387785.2210664721</v>
+        <v>387239</v>
       </c>
       <c r="R2" t="n">
-        <v>6723977.89326833</v>
+        <v>6723874</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-03-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-03-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>anders tedeholm, Helena Malmestrand</t>
+          <t>Andreas Larsson, Christina Svensson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>85440044</v>
+        <v>94037183</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,42 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>SO om Villmyren, Vrm</t>
+          <t>Sydväst om Branäsberget, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>387757.0972959037</v>
+        <v>387302</v>
       </c>
       <c r="R3" t="n">
-        <v>6723974.84390923</v>
+        <v>6723905</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-03-26</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-03-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,49 +857,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Christina Svensson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>anders tedeholm, Helena Malmestrand</t>
+          <t>Christina Svensson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>94037171</v>
+        <v>94036220</v>
       </c>
       <c r="B4" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>387222.3028684255</v>
+        <v>387330</v>
       </c>
       <c r="R4" t="n">
-        <v>6723887.503598205</v>
+        <v>6723896</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -977,19 +937,9 @@
           <t>2021-06-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-06-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,49 +954,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Christina Svensson</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Christina Svensson, Andreas Larsson</t>
+          <t>Andreas Larsson, Christina Svensson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>94036229</v>
+        <v>94037166</v>
       </c>
       <c r="B5" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>387239.5729223679</v>
+        <v>387032</v>
       </c>
       <c r="R5" t="n">
-        <v>6723873.706097425</v>
+        <v>6723842</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1089,19 +1034,9 @@
           <t>2021-06-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-06-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,27 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Christina Svensson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Christina Svensson</t>
+          <t>Christina Svensson, Andreas Larsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>94037166</v>
+        <v>94037167</v>
       </c>
       <c r="B6" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>387032.0548733314</v>
+        <v>387123</v>
       </c>
       <c r="R6" t="n">
-        <v>6723842.418225873</v>
+        <v>6723941</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1201,19 +1131,9 @@
           <t>2021-06-04</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-06-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,12 +1163,7 @@
         <v>94037168</v>
       </c>
       <c r="B7" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>387243.4271834774</v>
+        <v>387243</v>
       </c>
       <c r="R7" t="n">
-        <v>6723886.840891832</v>
+        <v>6723887</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1313,19 +1228,9 @@
           <t>2021-06-04</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-06-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,6 +1254,302 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>85440028</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>SO om Villmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>387785</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6723978</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-03-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-03-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>anders tedeholm, Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>94037171</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sydväst om Branäsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>387222</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6723888</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-06-04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-06-04</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Christina Svensson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Christina Svensson, Andreas Larsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>85440044</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>SO om Villmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>387757</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6723975</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2019-03-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2019-03-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>anders tedeholm, Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41279-2021 artfynd.xlsx
+++ b/artfynd/A 41279-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94036229</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94037183</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94036220</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94037166</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94037167</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94037168</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85440028</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94037171</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,8 +1595,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85440044</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>